--- a/daily_matches/job_matches_2026-05-25.xlsx
+++ b/daily_matches/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II, Pricing Engineering</t>
+          <t>Sr. Software Development Engineer 5.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>RAG, CI/CD, Jenkins, Git, Snowflake, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2bac108848ff31</t>
+          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, QA Automation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Protagona</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,441 +517,91 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Redshift, Kinesis, Snowflake, Databricks, Redshift</t>
+          <t>Data Scientist, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664ac749b66cbda9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a031e9a27e265a8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Java) in Test</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abeffb7fc3a2db5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5b8c611811b76b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Computer Vision Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sarasota Electrical</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, Docker, Kubernetes, Git, Python, R</t>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c549886f47434e</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior AI Application Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Channel Partners</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4916b9ca74608f73</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FastAPI, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35300f03b65d60e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Founding Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CLERA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, MySQL, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7fa6df8e3b4cf6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI IMPLEMENTATION ENGINEER</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Fitness Ventures LLC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Altamonte Springs, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, spaCy, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12c9cac91c56f549</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II, 3rd Party Fulfillment</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Wayfair</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8a84f415621d03</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data Engineer /Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Hadoop, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c45a5135dc266df2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Claude AI Specialist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DigitalShopper.com</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdbcaba39a8ea50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Jr. Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Focus Camera</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad988ce96b85a658</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Quality Engineering &amp; Surveying, LLC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Port Vincent, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3b6ebe206541ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DevSecOps Architect – CI/CD &amp; Application Security</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bce902bbb6e18b2</t>
+          <t>https://www.indeed.com/viewjob?jk=58dc15e425c40f04</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-25.xlsx
+++ b/daily_matches/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Sr Salesforce Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Snowflake, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc6430243b42499</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, QA Automation</t>
+          <t>Senior Full-Stack Engineer (US)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>ControlUp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,77 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a031e9a27e265a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AI Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5b8c611811b76b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58dc15e425c40f04</t>
+          <t>https://www.indeed.com/viewjob?jk=76dfe2ad78123859</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-25.xlsx
+++ b/daily_matches/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Salesforce Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc6430243b42499</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (US)</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ControlUp</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,21 +517,371 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=622e5174e22fc102</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AI Native Developer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=239176039e388a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI Native Developer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ac1dcfa7fd19426</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Moorestown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, Docker, Git, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13a4a4f5adcc9bb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Referral Only - Senior GCP Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf680fe82a439641</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, XGBoost, LightGBM, CatBoost, MLflow, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b630826288e449b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior NodeJS Backend Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd99560c4288f471</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Junior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, CI/CD, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76dfe2ad78123859</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c8aec45c1a01968</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DataArt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Apache Airflow, Snowflake, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Panasonic Automotive</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=537e07b46630008e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-25.xlsx
+++ b/daily_matches/job_matches_2026-05-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,33 +482,33 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Synapse, Data Lake, Kinesis, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=c207b60a85c3ae78</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,357 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622e5174e22fc102</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AI Native Developer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=239176039e388a7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Native Developer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac1dcfa7fd19426</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AI Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Moorestown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, OpenCV, Docker, Git, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13a4a4f5adcc9bb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Referral Only - Senior GCP Data Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, FastAPI, CI/CD, Git, BigQuery</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf680fe82a439641</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Affirm</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, XGBoost, LightGBM, CatBoost, MLflow, Python, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b630826288e449b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior NodeJS Backend Developer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd99560c4288f471</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Junior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8aec45c1a01968</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DataArt</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Apache Airflow, Snowflake, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Panasonic Automotive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=537e07b46630008e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a1142bdc6ff993</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-25.xlsx
+++ b/daily_matches/job_matches_2026-05-25.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Applied AI Engineer - AI Agent (New Graduate)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Synapse, Data Lake, Kinesis, CI/CD</t>
+          <t>AI Engineer, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c207b60a85c3ae78</t>
+          <t>https://www.indeed.com/viewjob?jk=cd520d2c56a639ea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Docker, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a1142bdc6ff993</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb36ff32f2f14d1</t>
         </is>
       </c>
     </row>
